--- a/aReport_card/2025_2026/First_term/JSS1/First_term_JSS1_2025_2026.xlsx
+++ b/aReport_card/2025_2026/First_term/JSS1/First_term_JSS1_2025_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Reporter\aReport_card\2025_2026\First_term\JSS1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C94EB8C3-F635-44DA-9143-D7D7292A3D5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39ECF4E6-7E06-4B68-9D64-860A25F4F182}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
